--- a/SpingGame_2026.xlsx
+++ b/SpingGame_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SakamotoKou\Documents\GitHub\SpringGame_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SakamotoKou\Desktop\GitHub\SpringGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6DD4D11-8B44-45CA-A3C8-1E97E5C87F2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF3A16AB-1A4B-446A-B00F-6BD15CC97F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-285" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{FD95E878-465A-49E4-912E-7153328F4E6C}"/>
+    <workbookView xWindow="-285" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{FD95E878-465A-49E4-912E-7153328F4E6C}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="74">
   <si>
     <t>2026年春作品コスト表</t>
     <rPh sb="4" eb="5">
@@ -484,13 +484,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Transformを反映する</t>
-    <rPh sb="10" eb="12">
-      <t>ハンエイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>生きているか</t>
     <rPh sb="0" eb="1">
       <t>イ</t>
@@ -563,6 +556,26 @@
   </si>
   <si>
     <t>ターゲット</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Transformを反映する,位置を取得する</t>
+    <rPh sb="10" eb="12">
+      <t>ハンエイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>シュトク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作業中</t>
+    <rPh sb="0" eb="3">
+      <t>サギョウチュウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3017,10 +3030,12 @@
       <c r="E4" s="22">
         <v>1</v>
       </c>
-      <c r="F4" s="22"/>
+      <c r="F4" s="22">
+        <v>1</v>
+      </c>
       <c r="G4" s="22" t="str">
         <f>IF(E4=F4,"完成",IF(F4="作業中","作業中","未着手"))</f>
-        <v>未着手</v>
+        <v>完成</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>29</v>
@@ -3081,7 +3096,7 @@
       </c>
       <c r="J6" s="11">
         <f>J4-SUM(F4:F25)</f>
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -3100,10 +3115,12 @@
       <c r="E7" s="16">
         <v>2</v>
       </c>
-      <c r="F7" s="16"/>
+      <c r="F7" s="16" t="s">
+        <v>73</v>
+      </c>
       <c r="G7" s="16" t="str">
         <f t="shared" si="0"/>
-        <v>未着手</v>
+        <v>作業中</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -3205,7 +3222,7 @@
       </c>
       <c r="J11" s="11">
         <f>J10-SUMIF($D$4:$D$25,$I9,$F$4:$F$25)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -3871,7 +3888,7 @@
     <col min="1" max="1" width="13.875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="56.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="33.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
@@ -3901,10 +3918,10 @@
         <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
@@ -3915,7 +3932,7 @@
         <v>61</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
@@ -3926,10 +3943,10 @@
         <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
@@ -3940,21 +3957,21 @@
         <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" t="s">
         <v>68</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>69</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>70</v>
-      </c>
-      <c r="D9" t="s">
-        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/SpingGame_2026.xlsx
+++ b/SpingGame_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SakamotoKou\Desktop\GitHub\SpringGame_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\SpringGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF3A16AB-1A4B-446A-B00F-6BD15CC97F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCBE22BE-C502-4B0C-B9D6-72F2A9072BF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-285" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{FD95E878-465A-49E4-912E-7153328F4E6C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FD95E878-465A-49E4-912E-7153328F4E6C}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="73">
   <si>
     <t>2026年春作品コスト表</t>
     <rPh sb="4" eb="5">
@@ -568,13 +568,6 @@
     </rPh>
     <rPh sb="18" eb="20">
       <t>シュトク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>作業中</t>
-    <rPh sb="0" eb="3">
-      <t>サギョウチュウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -963,7 +956,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="11">
     <dxf>
@@ -2636,7 +2629,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4B53FD9C-E324-4EF9-8E6E-0F8C6FCF9D02}" name="Table1" displayName="Table1" ref="A3:G25" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
-  <autoFilter ref="A3:G25" xr:uid="{4B53FD9C-E324-4EF9-8E6E-0F8C6FCF9D02}"/>
+  <autoFilter ref="A3:G25" xr:uid="{4B53FD9C-E324-4EF9-8E6E-0F8C6FCF9D02}">
+    <filterColumn colId="6">
+      <filters>
+        <filter val="未着手"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{E97F4431-85C6-4E77-984B-5FA78DBB96B6}" name="概要" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{80B497E9-6CB6-4288-83FB-ACB8F71DC7EB}" name="詳細" dataDxfId="5"/>
@@ -2653,7 +2652,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -3014,7 +3013,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.4">
       <c r="A4" s="16" t="s">
         <v>2</v>
       </c>
@@ -3045,7 +3044,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="16"/>
       <c r="B5" s="16" t="s">
         <v>8</v>
@@ -3072,7 +3071,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="16"/>
       <c r="B6" s="16" t="s">
         <v>15</v>
@@ -3086,20 +3085,22 @@
       <c r="E6" s="16">
         <v>0.5</v>
       </c>
-      <c r="F6" s="16"/>
+      <c r="F6" s="16">
+        <v>0.5</v>
+      </c>
       <c r="G6" s="16" t="str">
         <f t="shared" si="0"/>
-        <v>未着手</v>
+        <v>完成</v>
       </c>
       <c r="I6" s="10" t="s">
         <v>32</v>
       </c>
       <c r="J6" s="11">
         <f>J4-SUM(F4:F25)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="16" t="s">
         <v>9</v>
       </c>
@@ -3115,15 +3116,15 @@
       <c r="E7" s="16">
         <v>2</v>
       </c>
-      <c r="F7" s="16" t="s">
-        <v>73</v>
+      <c r="F7" s="16">
+        <v>2</v>
       </c>
       <c r="G7" s="16" t="str">
         <f t="shared" si="0"/>
-        <v>作業中</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>完成</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="16"/>
       <c r="B8" s="16" t="s">
         <v>10</v>
@@ -3137,10 +3138,12 @@
       <c r="E8" s="16">
         <v>2</v>
       </c>
-      <c r="F8" s="16"/>
+      <c r="F8" s="16">
+        <v>2</v>
+      </c>
       <c r="G8" s="16" t="str">
         <f t="shared" si="0"/>
-        <v>未着手</v>
+        <v>完成</v>
       </c>
       <c r="I8" s="23" t="s">
         <v>36</v>
@@ -3222,7 +3225,7 @@
       </c>
       <c r="J11" s="11">
         <f>J10-SUMIF($D$4:$D$25,$I9,$F$4:$F$25)</f>
-        <v>9</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">

--- a/SpingGame_2026.xlsx
+++ b/SpingGame_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\SpringGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCBE22BE-C502-4B0C-B9D6-72F2A9072BF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A024702-128A-4A5E-9463-C7256AE950AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FD95E878-465A-49E4-912E-7153328F4E6C}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="74">
   <si>
     <t>2026年春作品コスト表</t>
     <rPh sb="4" eb="5">
@@ -569,6 +569,10 @@
     <rPh sb="18" eb="20">
       <t>シュトク</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2629,13 +2633,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4B53FD9C-E324-4EF9-8E6E-0F8C6FCF9D02}" name="Table1" displayName="Table1" ref="A3:G25" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
-  <autoFilter ref="A3:G25" xr:uid="{4B53FD9C-E324-4EF9-8E6E-0F8C6FCF9D02}">
-    <filterColumn colId="6">
-      <filters>
-        <filter val="未着手"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A3:G25" xr:uid="{4B53FD9C-E324-4EF9-8E6E-0F8C6FCF9D02}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{E97F4431-85C6-4E77-984B-5FA78DBB96B6}" name="概要" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{80B497E9-6CB6-4288-83FB-ACB8F71DC7EB}" name="詳細" dataDxfId="5"/>
@@ -3013,7 +3011,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4" s="16" t="s">
         <v>2</v>
       </c>
@@ -3044,7 +3042,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5" s="16"/>
       <c r="B5" s="16" t="s">
         <v>8</v>
@@ -3071,7 +3069,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="16"/>
       <c r="B6" s="16" t="s">
         <v>15</v>
@@ -3100,7 +3098,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="16" t="s">
         <v>9</v>
       </c>
@@ -3124,7 +3122,7 @@
         <v>完成</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="16"/>
       <c r="B8" s="16" t="s">
         <v>10</v>
@@ -3194,7 +3192,7 @@
         <v>未着手</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="J10" s="7">
         <f>SUMIF($D$4:$D$25,$I9,$E$4:$E$25)</f>

--- a/SpingGame_2026.xlsx
+++ b/SpingGame_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\SpringGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A024702-128A-4A5E-9463-C7256AE950AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D81D698D-0641-48AE-9925-BC8864688ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FD95E878-465A-49E4-912E-7153328F4E6C}"/>
+    <workbookView xWindow="4725" yWindow="375" windowWidth="19605" windowHeight="15585" tabRatio="460" xr2:uid="{FD95E878-465A-49E4-912E-7153328F4E6C}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="76">
   <si>
     <t>2026年春作品コスト表</t>
     <rPh sb="4" eb="5">
@@ -573,6 +573,32 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Animation</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーや敵のアニメーションを行う際に再生・停止などを行わせる</t>
+    <rPh sb="6" eb="7">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>サイセイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>テイシ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>オコナ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1182,278 +1208,32 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>458326</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>159091</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>467353</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>305572</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>197191</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>56060</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>77053</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Arrow: Right 2">
+        <xdr:cNvPr id="35" name="Arrow: Right 24">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D01E877E-2A8C-BDFA-FC85-FE889904E537}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A135B934-ED09-4E6B-933C-35C9CBC7E8FB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
-        <a:xfrm rot="8791336">
-          <a:off x="1141498" y="1341505"/>
-          <a:ext cx="3263108" cy="274583"/>
-        </a:xfrm>
-        <a:prstGeom prst="rightArrow">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>205280</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>99191</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>386255</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>192799</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="Rectangle 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E51F130-21CC-4FF4-962A-70E4964537B4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="205280" y="2464019"/>
-          <a:ext cx="1547320" cy="566573"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent6">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent6"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent6"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
-            <a:t>Player</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>238123</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>180976</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>514348</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>45983</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="Arrow: Right 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97BF8ACD-94F4-4DED-A5E2-E775A4B75260}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="5400000">
-          <a:off x="3360353" y="1394263"/>
-          <a:ext cx="2229834" cy="276225"/>
-        </a:xfrm>
-        <a:prstGeom prst="rightArrow">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>314325</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>228600</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="Rectangle 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A20F885-6F78-4469-822C-6E7F839461ED}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3743325" y="2752725"/>
-          <a:ext cx="1552575" cy="571500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent6">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent6"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent6"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
-            <a:t>Enemy</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>634292</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>112454</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>548467</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>150554</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="Arrow: Right 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{412D9D80-9321-46AB-BECC-47D2F7DCE605}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="1808490">
-          <a:off x="4749092" y="826829"/>
-          <a:ext cx="2657375" cy="276225"/>
+        <a:xfrm rot="8097965">
+          <a:off x="3562533" y="2373291"/>
+          <a:ext cx="5018847" cy="272265"/>
         </a:xfrm>
         <a:prstGeom prst="rightArrow">
           <a:avLst/>
@@ -1489,15 +1269,195 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>361951</xdr:colOff>
+      <xdr:colOff>120773</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:rowOff>242071</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>542926</xdr:colOff>
+      <xdr:colOff>159070</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:rowOff>35241</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Arrow: Right 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D01E877E-2A8C-BDFA-FC85-FE889904E537}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="8381235">
+          <a:off x="6924344" y="1956571"/>
+          <a:ext cx="1399012" cy="283027"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>173780</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>53410</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>450005</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>123267</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Arrow: Right 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97BF8ACD-94F4-4DED-A5E2-E775A4B75260}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="7538376" y="2538785"/>
+          <a:ext cx="1952445" cy="276225"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>585680</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>232072</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>175544</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>51703</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Arrow: Right 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{412D9D80-9321-46AB-BECC-47D2F7DCE605}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="2971682">
+          <a:off x="8875209" y="2005426"/>
+          <a:ext cx="1466895" cy="273423"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>394354</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>200832</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>575329</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>59599</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1512,8 +1472,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7219951" y="1695450"/>
-          <a:ext cx="1552575" cy="571500"/>
+          <a:off x="9280619" y="2554067"/>
+          <a:ext cx="1548092" cy="564738"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1551,16 +1511,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>323850</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>259507</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>5786</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>228600</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>440482</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>101037</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1575,8 +1535,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3752850" y="133350"/>
-          <a:ext cx="1552575" cy="571500"/>
+          <a:off x="7743436" y="1475357"/>
+          <a:ext cx="1541689" cy="585109"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1614,23 +1574,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>649178</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>106417</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>70045</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>45007</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>520591</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>154042</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>631542</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>90988</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="TextBox 10">
+        <xdr:cNvPr id="12" name="TextBox 11">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F518418-F3E4-79B6-743D-B8DB60EF88FD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5E2E3BD-9CCA-4EA5-B777-5FBF338CAFEE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1638,8 +1598,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3381868" y="815865"/>
-          <a:ext cx="554585" cy="284108"/>
+          <a:off x="8272751" y="2868889"/>
+          <a:ext cx="561497" cy="281305"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1675,7 +1635,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="1">
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
@@ -1689,23 +1649,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>71437</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>228600</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>491863</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>212761</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>628650</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>358992</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>18549</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="TextBox 11">
+        <xdr:cNvPr id="13" name="TextBox 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5E2E3BD-9CCA-4EA5-B777-5FBF338CAFEE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD633AA0-7B76-4242-A973-C6617CF77E8C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1713,8 +1673,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4186237" y="942975"/>
-          <a:ext cx="557213" cy="285750"/>
+          <a:off x="9378128" y="2095349"/>
+          <a:ext cx="550688" cy="276435"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1750,82 +1710,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>継承</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>114793</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>213162</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>669378</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>22663</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="TextBox 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD633AA0-7B76-4242-A973-C6617CF77E8C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5580172" y="686128"/>
-          <a:ext cx="554585" cy="282466"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="1">
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
@@ -1894,16 +1779,16 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>358836</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>85583</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>189871</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>124607</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>841</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>123683</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>112157</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>162706</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1917,9 +1802,9 @@
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
-        <a:xfrm rot="13268339">
-          <a:off x="1725181" y="2923376"/>
-          <a:ext cx="1008350" cy="274583"/>
+        <a:xfrm rot="21186054">
+          <a:off x="4291224" y="4360431"/>
+          <a:ext cx="3340080" cy="273422"/>
         </a:xfrm>
         <a:prstGeom prst="rightArrow">
           <a:avLst/>
@@ -1954,16 +1839,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>624507</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>185173</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>656662</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>145342</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>360514</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>224915</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>256765</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>180214</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1977,9 +1862,9 @@
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
-        <a:xfrm rot="19570956">
-          <a:off x="2674024" y="3022966"/>
-          <a:ext cx="1102352" cy="276225"/>
+        <a:xfrm rot="18983565">
+          <a:off x="4758015" y="3675195"/>
+          <a:ext cx="1650779" cy="270195"/>
         </a:xfrm>
         <a:prstGeom prst="rightArrow">
           <a:avLst/>
@@ -2014,16 +1899,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>285421</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>209551</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>437750</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>160558</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>228271</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>190501</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>96322</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>44823</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2038,8 +1923,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1651766" y="3283827"/>
-          <a:ext cx="1992367" cy="690398"/>
+          <a:off x="3171985" y="4396382"/>
+          <a:ext cx="1709249" cy="590235"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2067,14 +1952,14 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400"/>
             <a:t>Collision</a:t>
           </a:r>
         </a:p>
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400"/>
             <a:t>Manager</a:t>
           </a:r>
         </a:p>
@@ -2084,16 +1969,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>360099</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>135525</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>328498</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>169379</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>157654</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>124810</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>121767</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>163537</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2108,8 +1993,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3092789" y="2973318"/>
-          <a:ext cx="480727" cy="225768"/>
+          <a:off x="5113410" y="3934555"/>
+          <a:ext cx="476828" cy="229482"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2145,7 +2030,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
@@ -2159,16 +2044,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>532206</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>58012</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>341404</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>136300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>329761</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>47297</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>134675</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>125586</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2183,8 +2068,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1898551" y="2895805"/>
-          <a:ext cx="480727" cy="225768"/>
+          <a:off x="5809875" y="4372124"/>
+          <a:ext cx="476829" cy="224609"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2220,7 +2105,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
@@ -2234,16 +2119,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>211417</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>157256</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>417239</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>171615</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>487642</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>115057</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>290883</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>215718</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2257,9 +2142,9 @@
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
-        <a:xfrm rot="6869262">
-          <a:off x="4679871" y="2126388"/>
-          <a:ext cx="903732" cy="276225"/>
+        <a:xfrm rot="10172058">
+          <a:off x="9303504" y="3701468"/>
+          <a:ext cx="2607879" cy="279426"/>
         </a:xfrm>
         <a:prstGeom prst="rightArrow">
           <a:avLst/>
@@ -2294,16 +2179,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>144637</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>18597</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>221028</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>164439</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>625364</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>7882</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>21397</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>153725</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2318,8 +2203,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4926844" y="2146942"/>
-          <a:ext cx="480727" cy="225768"/>
+          <a:off x="10474410" y="3694292"/>
+          <a:ext cx="483928" cy="224609"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2355,7 +2240,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
@@ -2369,16 +2254,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>142218</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>32844</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>66598</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>37533</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>320565</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>128094</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>244945</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>131624</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2393,8 +2278,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4924425" y="1451741"/>
-          <a:ext cx="1544692" cy="568215"/>
+          <a:off x="11687098" y="3332062"/>
+          <a:ext cx="1545465" cy="564738"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2432,16 +2317,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>79853</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>93327</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>655362</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>149200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>354436</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>58581</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>253873</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>213129</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2456,8 +2341,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm rot="5785265">
-          <a:off x="326483" y="1712283"/>
-          <a:ext cx="1147668" cy="274583"/>
+          <a:off x="7879367" y="898981"/>
+          <a:ext cx="798715" cy="278868"/>
         </a:xfrm>
         <a:prstGeom prst="rightArrow">
           <a:avLst/>
@@ -2492,79 +2377,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>502525</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>75543</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>575421</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>24869</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>328</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>372977</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>170793</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="24" name="Rectangle 23">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA817B95-F3CB-E4A9-6E00-5151DF776C7E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="502525" y="784991"/>
-          <a:ext cx="1547320" cy="568216"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent6">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent6"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent6"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
-            <a:t>SceneMain</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>14572</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>210411</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>495299</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>199697</xdr:rowOff>
+      <xdr:rowOff>14154</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2579,8 +2401,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="697744" y="1629308"/>
-          <a:ext cx="480727" cy="225768"/>
+          <a:off x="8059350" y="1004583"/>
+          <a:ext cx="477913" cy="234214"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2616,12 +2438,954 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
             </a:rPr>
             <a:t>実体</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>129898</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>138666</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>563665</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>175608</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="Arrow: Right 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6677502D-58A3-4656-AE4B-8892BA50CD9A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="9301400">
+          <a:off x="2864133" y="1315284"/>
+          <a:ext cx="5218679" cy="272265"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>290802</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>128880</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>92254</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>118165</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="TextBox 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E6D9CFE-6E3B-47C2-8DD9-3F729234D341}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5759273" y="1070174"/>
+          <a:ext cx="485010" cy="224609"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>実体</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>466783</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>235133</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>59217</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>38479</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="Arrow: Right 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C525A878-C8D0-4E9E-8EA5-8D1A7E565304}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000">
+          <a:off x="3884577" y="2823692"/>
+          <a:ext cx="2326669" cy="273993"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>433262</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>211634</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>359293</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>26085</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="TextBox 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{903B4AE0-5D43-4634-9D1E-23B43FF4D363}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="21445648">
+          <a:off x="4534615" y="2800193"/>
+          <a:ext cx="609590" cy="285098"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>参照</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>379025</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>136408</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>378715</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>184112</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="Arrow: Right 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C85E42A-F2B2-444C-AA4D-DEEEE5EB77BE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="11559552">
+          <a:off x="3796819" y="3430937"/>
+          <a:ext cx="4101043" cy="283028"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>425592</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>88939</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>408651</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>173790</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="30" name="TextBox 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9446D939-CB62-4FB3-9BD7-3DFBC55C0744}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6577621" y="3618792"/>
+          <a:ext cx="666618" cy="320174"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>参照</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>200975</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>143420</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>378052</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>4629</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="Rectangle 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E81D0E7-01DA-4F81-B113-DB8E6E639D5F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2251651" y="2731979"/>
+          <a:ext cx="1544195" cy="567179"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+            <a:t>Animation</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>206690</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>198199</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>390865</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>58125</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Rectangle 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A20F885-6F78-4469-822C-6E7F839461ED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7725837" y="3728052"/>
+          <a:ext cx="1551293" cy="565897"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+            <a:t>Enemy</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>117193</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>36069</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>483151</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>78902</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="31" name="Arrow: Right 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{526A6896-B434-496B-93CA-451F518825FC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="2314216">
+          <a:off x="8319899" y="1683334"/>
+          <a:ext cx="4467311" cy="278156"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>255250</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>131615</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>52804</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>120900</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="32" name="TextBox 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93EB9AA4-93F2-464E-9E79-3571AA958905}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9780250" y="1356258"/>
+          <a:ext cx="477911" cy="234213"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>実体</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>397193</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>180492</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>268604</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>232850</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="TextBox 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F518418-F3E4-79B6-743D-B8DB60EF88FD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7200764" y="2139921"/>
+          <a:ext cx="551769" cy="297286"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>継承</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>429846</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>190498</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>231297</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>179784</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="36" name="TextBox 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C9E3DB3F-7310-4EBE-9877-3D99337ECCC9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4531199" y="3720351"/>
+          <a:ext cx="485010" cy="224609"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>実体</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>504679</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>234610</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>5296</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>83290</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Rectangle 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E51F130-21CC-4FF4-962A-70E4964537B4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5947536" y="2683896"/>
+          <a:ext cx="1541689" cy="583465"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+            <a:t>Player</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>662995</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>55652</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>163613</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>150902</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="Rectangle 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA817B95-F3CB-E4A9-6E00-5151DF776C7E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7466566" y="300581"/>
+          <a:ext cx="1541690" cy="585107"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+            <a:t>SceneMain</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -3713,11 +4477,11 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A8" s="2">
+      <c r="A8" s="1">
         <f>G7+1</f>
         <v>29</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="1">
         <f>A8+1</f>
         <v>30</v>
       </c>
@@ -3871,9 +4635,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50D97A9B-22C3-4B91-B60B-CE8D4AC2A40C}">
-  <dimension ref="A1"/>
+  <dimension ref="C9"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData/>
+  <sheetData>
+    <row r="9" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3883,11 +4653,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F0E7A76-8688-4F39-8068-49EB5686174C}">
-  <dimension ref="A3:D9"/>
+  <dimension ref="A3:D10"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="56.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="66.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="33.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="35.25" bestFit="1" customWidth="1"/>
   </cols>
@@ -3973,6 +4743,14 @@
       </c>
       <c r="D9" t="s">
         <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/SpingGame_2026.xlsx
+++ b/SpingGame_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\SpringGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D81D698D-0641-48AE-9925-BC8864688ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51F51B48-8B8F-46DD-8AFD-4EDA7F3BC013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4725" yWindow="375" windowWidth="19605" windowHeight="15585" tabRatio="460" xr2:uid="{FD95E878-465A-49E4-912E-7153328F4E6C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="460" xr2:uid="{FD95E878-465A-49E4-912E-7153328F4E6C}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="78">
   <si>
     <t>2026年春作品コスト表</t>
     <rPh sb="4" eb="5">
@@ -598,6 +598,20 @@
     </rPh>
     <rPh sb="28" eb="29">
       <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーの移動</t>
+    <rPh sb="6" eb="8">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーの待機</t>
+    <rPh sb="6" eb="8">
+      <t>タイキ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -896,7 +910,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -982,6 +996,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3396,8 +3413,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4B53FD9C-E324-4EF9-8E6E-0F8C6FCF9D02}" name="Table1" displayName="Table1" ref="A3:G25" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
-  <autoFilter ref="A3:G25" xr:uid="{4B53FD9C-E324-4EF9-8E6E-0F8C6FCF9D02}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4B53FD9C-E324-4EF9-8E6E-0F8C6FCF9D02}" name="Table1" displayName="Table1" ref="A3:G27" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
+  <autoFilter ref="A3:G27" xr:uid="{4B53FD9C-E324-4EF9-8E6E-0F8C6FCF9D02}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{E97F4431-85C6-4E77-984B-5FA78DBB96B6}" name="概要" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{80B497E9-6CB6-4288-83FB-ACB8F71DC7EB}" name="詳細" dataDxfId="5"/>
@@ -3730,7 +3747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C89A4258-94D6-44E2-BD96-6EB7C71AF1F2}">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
@@ -3802,8 +3819,8 @@
         <v>29</v>
       </c>
       <c r="J4" s="7">
-        <f>SUM(E4:E25)</f>
-        <v>21</v>
+        <f>SUM(E4:E27)</f>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.4">
@@ -3820,17 +3837,19 @@
       <c r="E5" s="16">
         <v>1</v>
       </c>
-      <c r="F5" s="16"/>
+      <c r="F5" s="16">
+        <v>1</v>
+      </c>
       <c r="G5" s="16" t="str">
-        <f t="shared" ref="G5:G25" si="0">IF(E5=F5,"完成",IF(F5="作業中","作業中","未着手"))</f>
-        <v>未着手</v>
+        <f t="shared" ref="G5:G27" si="0">IF(E5=F5,"完成",IF(F5="作業中","作業中","未着手"))</f>
+        <v>完成</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>30</v>
       </c>
       <c r="J5" s="9">
         <f>J4*3</f>
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -3858,8 +3877,8 @@
         <v>32</v>
       </c>
       <c r="J6" s="11">
-        <f>J4-SUM(F4:F25)</f>
-        <v>15.5</v>
+        <f>J4-SUM(F4:F27)</f>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -3959,7 +3978,7 @@
         <v>73</v>
       </c>
       <c r="J10" s="7">
-        <f>SUMIF($D$4:$D$25,$I9,$E$4:$E$25)</f>
+        <f>SUMIF($D$4:$D$27,$I9,$E$4:$E$27)</f>
         <v>10</v>
       </c>
     </row>
@@ -3986,8 +4005,8 @@
         <v>38</v>
       </c>
       <c r="J11" s="11">
-        <f>J10-SUMIF($D$4:$D$25,$I9,$F$4:$F$25)</f>
-        <v>4.5</v>
+        <f>J10-SUMIF($D$4:$D$27,$I9,$F$4:$F$27)</f>
+        <v>3.5</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -4058,8 +4077,8 @@
         <v>37</v>
       </c>
       <c r="J14" s="7">
-        <f>SUMIF($D$4:$D$25,$I13,$E$4:$E$25)</f>
-        <v>7</v>
+        <f>SUMIF($D$4:$D$27,$I13,$E$4:$E$27)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -4085,11 +4104,11 @@
         <v>38</v>
       </c>
       <c r="J15" s="11">
-        <f>J14-SUMIF($D$4:$D$25,$I13,$F$4:$F$25)</f>
-        <v>7</v>
+        <f>J14-SUMIF($D$4:$D$27,$I13,$F$4:$F$27)</f>
+        <v>4.5</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A16" s="16" t="s">
         <v>25</v>
       </c>
@@ -4105,19 +4124,21 @@
       <c r="E16" s="16">
         <v>1</v>
       </c>
-      <c r="F16" s="16"/>
+      <c r="F16" s="16">
+        <v>1</v>
+      </c>
       <c r="G16" s="16" t="str">
         <f t="shared" si="0"/>
-        <v>未着手</v>
+        <v>完成</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="16"/>
-      <c r="B17" s="16" t="s">
-        <v>27</v>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A17" s="29"/>
+      <c r="B17" s="29" t="s">
+        <v>76</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D17" s="18" t="s">
         <v>34</v>
@@ -4125,19 +4146,18 @@
       <c r="E17" s="16">
         <v>1</v>
       </c>
-      <c r="F17" s="16"/>
+      <c r="F17" s="16">
+        <v>1</v>
+      </c>
       <c r="G17" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>未着手</v>
-      </c>
-      <c r="I17" s="26" t="s">
-        <v>35</v>
+        <f>IF(E17=F17,"完成",IF(F17="作業中","作業中","未着手"))</f>
+        <v>完成</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A18" s="16"/>
-      <c r="B18" s="16" t="s">
-        <v>28</v>
+    <row r="18" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="29"/>
+      <c r="B18" s="29" t="s">
+        <v>77</v>
       </c>
       <c r="C18" s="16" t="s">
         <v>17</v>
@@ -4148,29 +4168,24 @@
       <c r="E18" s="16">
         <v>1</v>
       </c>
-      <c r="F18" s="16"/>
+      <c r="F18" s="16">
+        <v>1</v>
+      </c>
       <c r="G18" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>未着手</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="J18" s="7">
-        <f>SUMIF($D$4:$D$25,$I17,$E$4:$E$25)</f>
-        <v>4</v>
+        <f>IF(E18=F18,"完成",IF(F18="作業中","作業中","未着手"))</f>
+        <v>完成</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="16"/>
       <c r="B19" s="16" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>35</v>
+        <v>18</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>34</v>
       </c>
       <c r="E19" s="16">
         <v>1</v>
@@ -4180,20 +4195,14 @@
         <f t="shared" si="0"/>
         <v>未着手</v>
       </c>
-      <c r="I19" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="J19" s="11">
-        <f>J18-SUMIF($D$4:$D$25,$I17,$F$4:$F$25)</f>
-        <v>4</v>
+      <c r="I19" s="26" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="16" t="s">
-        <v>39</v>
-      </c>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A20" s="16"/>
       <c r="B20" s="16" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="C20" s="16" t="s">
         <v>17</v>
@@ -4202,124 +4211,186 @@
         <v>34</v>
       </c>
       <c r="E20" s="16">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F20" s="16"/>
       <c r="G20" s="16" t="str">
         <f t="shared" si="0"/>
         <v>未着手</v>
       </c>
+      <c r="I20" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="J20" s="7">
+        <f>SUMIF($D$4:$D$27,$I19,$E$4:$E$27)</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="16"/>
       <c r="B21" s="16" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>34</v>
+        <v>24</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>35</v>
       </c>
       <c r="E21" s="16">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F21" s="16"/>
       <c r="G21" s="16" t="str">
         <f t="shared" si="0"/>
         <v>未着手</v>
       </c>
-      <c r="I21" s="27" t="s">
+      <c r="I21" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="J21" s="11">
+        <f>J20-SUMIF($D$4:$D$27,$I19,$F$4:$F$27)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="F22" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="G22" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>完成</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="16"/>
+      <c r="B23" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="E23" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="F23" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="G23" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>完成</v>
+      </c>
+      <c r="I23" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="J21" s="28">
+      <c r="J23" s="28">
         <f>DATE(2026,4,13)-DATE(2026,3,17)</f>
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="16"/>
-      <c r="B22" s="16" t="s">
+    <row r="24" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="16"/>
+      <c r="B24" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C24" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="D24" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="E22" s="16">
+      <c r="E24" s="16">
         <v>0.5</v>
       </c>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16" t="str">
+      <c r="F24" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="G24" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>完成</v>
+      </c>
+      <c r="I24" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="J24" s="28">
+        <f>J4/J23</f>
+        <v>0.85185185185185186</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A25" s="16"/>
+      <c r="B25" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16" t="str">
         <f t="shared" si="0"/>
         <v>未着手</v>
       </c>
-      <c r="I22" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="J22" s="28">
-        <f>J4/J21</f>
-        <v>0.77777777777777779</v>
-      </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A23" s="16"/>
-      <c r="B23" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="D23" s="18" t="s">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A26" s="16"/>
+      <c r="B26" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="E23" s="16">
+      <c r="E26" s="16">
         <v>0.5</v>
       </c>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16" t="str">
+      <c r="F26" s="16"/>
+      <c r="G26" s="16" t="str">
         <f t="shared" si="0"/>
         <v>未着手</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A24" s="16"/>
-      <c r="B24" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="D24" s="18" t="s">
+    <row r="27" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="17"/>
+      <c r="B27" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="D27" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="E24" s="16">
+      <c r="E27" s="17">
         <v>0.5</v>
       </c>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>未着手</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="D25" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="E25" s="17">
-        <v>0.5</v>
-      </c>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17" t="str">
+      <c r="F27" s="17"/>
+      <c r="G27" s="17" t="str">
         <f t="shared" si="0"/>
         <v>未着手</v>
       </c>

--- a/SpingGame_2026.xlsx
+++ b/SpingGame_2026.xlsx
@@ -910,7 +910,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -996,9 +996,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4133,8 +4130,8 @@
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A17" s="29"/>
-      <c r="B17" s="29" t="s">
+      <c r="A17" s="16"/>
+      <c r="B17" s="16" t="s">
         <v>76</v>
       </c>
       <c r="C17" s="16" t="s">
@@ -4155,8 +4152,8 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="29"/>
-      <c r="B18" s="29" t="s">
+      <c r="A18" s="16"/>
+      <c r="B18" s="16" t="s">
         <v>77</v>
       </c>
       <c r="C18" s="16" t="s">

--- a/SpingGame_2026.xlsx
+++ b/SpingGame_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\SpringGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51F51B48-8B8F-46DD-8AFD-4EDA7F3BC013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67C818AB-865E-41A4-8ADD-616FADA50B66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="460" xr2:uid="{FD95E878-465A-49E4-912E-7153328F4E6C}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" tabRatio="460" xr2:uid="{FD95E878-465A-49E4-912E-7153328F4E6C}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -3411,7 +3411,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4B53FD9C-E324-4EF9-8E6E-0F8C6FCF9D02}" name="Table1" displayName="Table1" ref="A3:G27" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
-  <autoFilter ref="A3:G27" xr:uid="{4B53FD9C-E324-4EF9-8E6E-0F8C6FCF9D02}"/>
+  <autoFilter ref="A3:G27" xr:uid="{4B53FD9C-E324-4EF9-8E6E-0F8C6FCF9D02}">
+    <filterColumn colId="6">
+      <filters>
+        <filter val="未着手"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{E97F4431-85C6-4E77-984B-5FA78DBB96B6}" name="概要" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{80B497E9-6CB6-4288-83FB-ACB8F71DC7EB}" name="詳細" dataDxfId="5"/>
@@ -3789,7 +3795,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="16" t="s">
         <v>2</v>
       </c>
@@ -3820,7 +3826,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="16"/>
       <c r="B5" s="16" t="s">
         <v>8</v>
@@ -3849,7 +3855,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="16"/>
       <c r="B6" s="16" t="s">
         <v>15</v>
@@ -3875,10 +3881,10 @@
       </c>
       <c r="J6" s="11">
         <f>J4-SUM(F4:F27)</f>
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="16" t="s">
         <v>9</v>
       </c>
@@ -3902,7 +3908,7 @@
         <v>完成</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="16"/>
       <c r="B8" s="16" t="s">
         <v>10</v>
@@ -4003,10 +4009,10 @@
       </c>
       <c r="J11" s="11">
         <f>J10-SUMIF($D$4:$D$27,$I9,$F$4:$F$27)</f>
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:10" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A12" s="16"/>
       <c r="B12" s="16" t="s">
         <v>19</v>
@@ -4020,10 +4026,12 @@
       <c r="E12" s="16">
         <v>2</v>
       </c>
-      <c r="F12" s="16"/>
+      <c r="F12" s="16">
+        <v>2</v>
+      </c>
       <c r="G12" s="16" t="str">
         <f t="shared" si="0"/>
-        <v>未着手</v>
+        <v>完成</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -4105,7 +4113,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:10" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A16" s="16" t="s">
         <v>25</v>
       </c>
@@ -4129,7 +4137,7 @@
         <v>完成</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:10" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="16"/>
       <c r="B17" s="16" t="s">
         <v>76</v>
@@ -4151,7 +4159,7 @@
         <v>完成</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:10" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="16"/>
       <c r="B18" s="16" t="s">
         <v>77</v>
@@ -4250,7 +4258,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.4">
       <c r="A22" s="16" t="s">
         <v>39</v>
       </c>
@@ -4274,7 +4282,7 @@
         <v>完成</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:10" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="16"/>
       <c r="B23" s="16" t="s">
         <v>11</v>
@@ -4303,7 +4311,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:10" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A24" s="16"/>
       <c r="B24" s="16" t="s">
         <v>40</v>

--- a/SpingGame_2026.xlsx
+++ b/SpingGame_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\SpringGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67C818AB-865E-41A4-8ADD-616FADA50B66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7709D8B7-4FA7-4796-8CC6-A42F4C0655E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" tabRatio="460" xr2:uid="{FD95E878-465A-49E4-912E-7153328F4E6C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="460" xr2:uid="{FD95E878-465A-49E4-912E-7153328F4E6C}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -3411,13 +3411,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4B53FD9C-E324-4EF9-8E6E-0F8C6FCF9D02}" name="Table1" displayName="Table1" ref="A3:G27" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
-  <autoFilter ref="A3:G27" xr:uid="{4B53FD9C-E324-4EF9-8E6E-0F8C6FCF9D02}">
-    <filterColumn colId="6">
-      <filters>
-        <filter val="未着手"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A3:G27" xr:uid="{4B53FD9C-E324-4EF9-8E6E-0F8C6FCF9D02}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{E97F4431-85C6-4E77-984B-5FA78DBB96B6}" name="概要" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{80B497E9-6CB6-4288-83FB-ACB8F71DC7EB}" name="詳細" dataDxfId="5"/>
@@ -3795,7 +3789,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4" s="16" t="s">
         <v>2</v>
       </c>
@@ -3826,7 +3820,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5" s="16"/>
       <c r="B5" s="16" t="s">
         <v>8</v>
@@ -3855,7 +3849,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="16"/>
       <c r="B6" s="16" t="s">
         <v>15</v>
@@ -3881,10 +3875,10 @@
       </c>
       <c r="J6" s="11">
         <f>J4-SUM(F4:F27)</f>
-        <v>10</v>
+        <v>7.5</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="16" t="s">
         <v>9</v>
       </c>
@@ -3908,7 +3902,7 @@
         <v>完成</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="16"/>
       <c r="B8" s="16" t="s">
         <v>10</v>
@@ -3949,10 +3943,12 @@
       <c r="E9" s="16">
         <v>1</v>
       </c>
-      <c r="F9" s="16"/>
+      <c r="F9" s="16">
+        <v>1</v>
+      </c>
       <c r="G9" s="16" t="str">
         <f t="shared" si="0"/>
-        <v>未着手</v>
+        <v>完成</v>
       </c>
       <c r="I9" s="24" t="s">
         <v>33</v>
@@ -3972,10 +3968,12 @@
       <c r="E10" s="16">
         <v>1</v>
       </c>
-      <c r="F10" s="16"/>
+      <c r="F10" s="16">
+        <v>1</v>
+      </c>
       <c r="G10" s="16" t="str">
         <f t="shared" si="0"/>
-        <v>未着手</v>
+        <v>完成</v>
       </c>
       <c r="I10" s="6" t="s">
         <v>73</v>
@@ -3999,20 +3997,22 @@
       <c r="E11" s="16">
         <v>0.5</v>
       </c>
-      <c r="F11" s="16"/>
+      <c r="F11" s="16">
+        <v>0.5</v>
+      </c>
       <c r="G11" s="16" t="str">
         <f t="shared" si="0"/>
-        <v>未着手</v>
+        <v>完成</v>
       </c>
       <c r="I11" s="10" t="s">
         <v>38</v>
       </c>
       <c r="J11" s="11">
         <f>J10-SUMIF($D$4:$D$27,$I9,$F$4:$F$27)</f>
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A12" s="16"/>
       <c r="B12" s="16" t="s">
         <v>19</v>
@@ -4110,10 +4110,10 @@
       </c>
       <c r="J15" s="11">
         <f>J14-SUMIF($D$4:$D$27,$I13,$F$4:$F$27)</f>
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A16" s="16" t="s">
         <v>25</v>
       </c>
@@ -4137,7 +4137,7 @@
         <v>完成</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A17" s="16"/>
       <c r="B17" s="16" t="s">
         <v>76</v>
@@ -4159,7 +4159,7 @@
         <v>完成</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="16"/>
       <c r="B18" s="16" t="s">
         <v>77</v>
@@ -4258,7 +4258,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="16" t="s">
         <v>39</v>
       </c>
@@ -4282,7 +4282,7 @@
         <v>完成</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="16"/>
       <c r="B23" s="16" t="s">
         <v>11</v>
@@ -4311,7 +4311,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A24" s="16"/>
       <c r="B24" s="16" t="s">
         <v>40</v>

--- a/SpingGame_2026.xlsx
+++ b/SpingGame_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\SpringGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7709D8B7-4FA7-4796-8CC6-A42F4C0655E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91610C2B-2205-44AE-8CF2-FA1D6D7DF24F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="460" xr2:uid="{FD95E878-465A-49E4-912E-7153328F4E6C}"/>
   </bookViews>
@@ -3875,7 +3875,7 @@
       </c>
       <c r="J6" s="11">
         <f>J4-SUM(F4:F27)</f>
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="J15" s="11">
         <f>J14-SUMIF($D$4:$D$27,$I13,$F$4:$F$27)</f>
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.4">
@@ -4195,10 +4195,12 @@
       <c r="E19" s="16">
         <v>1</v>
       </c>
-      <c r="F19" s="16"/>
+      <c r="F19" s="16">
+        <v>1</v>
+      </c>
       <c r="G19" s="16" t="str">
         <f t="shared" si="0"/>
-        <v>未着手</v>
+        <v>完成</v>
       </c>
       <c r="I19" s="26" t="s">
         <v>35</v>
@@ -4218,10 +4220,12 @@
       <c r="E20" s="16">
         <v>1</v>
       </c>
-      <c r="F20" s="16"/>
+      <c r="F20" s="16">
+        <v>1</v>
+      </c>
       <c r="G20" s="16" t="str">
         <f t="shared" si="0"/>
-        <v>未着手</v>
+        <v>完成</v>
       </c>
       <c r="I20" s="6" t="s">
         <v>37</v>
@@ -4354,10 +4358,12 @@
       <c r="E25" s="16">
         <v>0.5</v>
       </c>
-      <c r="F25" s="16"/>
+      <c r="F25" s="16">
+        <v>0.5</v>
+      </c>
       <c r="G25" s="16" t="str">
         <f t="shared" si="0"/>
-        <v>未着手</v>
+        <v>完成</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.4">
@@ -4374,10 +4380,12 @@
       <c r="E26" s="16">
         <v>0.5</v>
       </c>
-      <c r="F26" s="16"/>
+      <c r="F26" s="16">
+        <v>0.5</v>
+      </c>
       <c r="G26" s="16" t="str">
         <f t="shared" si="0"/>
-        <v>未着手</v>
+        <v>完成</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">

--- a/SpingGame_2026.xlsx
+++ b/SpingGame_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\SpringGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91610C2B-2205-44AE-8CF2-FA1D6D7DF24F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D832D17C-0AFB-41CE-B252-5B4146758017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="460" xr2:uid="{FD95E878-465A-49E4-912E-7153328F4E6C}"/>
   </bookViews>
@@ -3875,7 +3875,7 @@
       </c>
       <c r="J6" s="11">
         <f>J4-SUM(F4:F27)</f>
-        <v>4.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -4050,10 +4050,12 @@
       <c r="E13" s="16">
         <v>1</v>
       </c>
-      <c r="F13" s="16"/>
+      <c r="F13" s="16">
+        <v>1</v>
+      </c>
       <c r="G13" s="16" t="str">
         <f t="shared" si="0"/>
-        <v>未着手</v>
+        <v>完成</v>
       </c>
       <c r="I13" s="25" t="s">
         <v>34</v>
@@ -4073,10 +4075,12 @@
       <c r="E14" s="16">
         <v>1</v>
       </c>
-      <c r="F14" s="16"/>
+      <c r="F14" s="16">
+        <v>1</v>
+      </c>
       <c r="G14" s="16" t="str">
         <f t="shared" si="0"/>
-        <v>未着手</v>
+        <v>完成</v>
       </c>
       <c r="I14" s="6" t="s">
         <v>37</v>
@@ -4100,17 +4104,19 @@
       <c r="E15" s="16">
         <v>1</v>
       </c>
-      <c r="F15" s="16"/>
+      <c r="F15" s="16">
+        <v>1</v>
+      </c>
       <c r="G15" s="16" t="str">
         <f t="shared" si="0"/>
-        <v>未着手</v>
+        <v>完成</v>
       </c>
       <c r="I15" s="10" t="s">
         <v>38</v>
       </c>
       <c r="J15" s="11">
         <f>J14-SUMIF($D$4:$D$27,$I13,$F$4:$F$27)</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.4">
@@ -4249,17 +4255,19 @@
       <c r="E21" s="16">
         <v>1</v>
       </c>
-      <c r="F21" s="16"/>
+      <c r="F21" s="16">
+        <v>1</v>
+      </c>
       <c r="G21" s="16" t="str">
         <f t="shared" si="0"/>
-        <v>未着手</v>
+        <v>完成</v>
       </c>
       <c r="I21" s="10" t="s">
         <v>38</v>
       </c>
       <c r="J21" s="11">
         <f>J20-SUMIF($D$4:$D$27,$I19,$F$4:$F$27)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -4402,10 +4410,12 @@
       <c r="E27" s="17">
         <v>0.5</v>
       </c>
-      <c r="F27" s="17"/>
+      <c r="F27" s="16">
+        <v>0.5</v>
+      </c>
       <c r="G27" s="17" t="str">
         <f t="shared" si="0"/>
-        <v>未着手</v>
+        <v>完成</v>
       </c>
     </row>
   </sheetData>

--- a/SpingGame_2026.xlsx
+++ b/SpingGame_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\SpringGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D832D17C-0AFB-41CE-B252-5B4146758017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BE663FE-17EE-4D21-BBF2-D886106072BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="460" xr2:uid="{FD95E878-465A-49E4-912E-7153328F4E6C}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="79">
   <si>
     <t>2026年春作品コスト表</t>
     <rPh sb="4" eb="5">
@@ -612,6 +612,13 @@
     <t>プレイヤーの待機</t>
     <rPh sb="6" eb="8">
       <t>タイキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>春作品ブラッシュアップ</t>
+    <rPh sb="0" eb="3">
+      <t>ハルサクヒン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3744,7 +3751,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C89A4258-94D6-44E2-BD96-6EB7C71AF1F2}">
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
@@ -4416,6 +4423,11 @@
       <c r="G27" s="17" t="str">
         <f t="shared" si="0"/>
         <v>完成</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/SpingGame_2026.xlsx
+++ b/SpingGame_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\SpringGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BE663FE-17EE-4D21-BBF2-D886106072BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E508BE5-8032-4E84-BBFC-6394977E33AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="460" xr2:uid="{FD95E878-465A-49E4-912E-7153328F4E6C}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="89">
   <si>
     <t>2026年春作品コスト表</t>
     <rPh sb="4" eb="5">
@@ -616,9 +616,85 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>春作品ブラッシュアップ</t>
-    <rPh sb="0" eb="3">
-      <t>ハルサクヒン</t>
+    <t>インターン作品</t>
+    <rPh sb="5" eb="7">
+      <t>サクヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ベヨネッタ模倣に向けたゲームの準備的な感じ</t>
+    <rPh sb="5" eb="7">
+      <t>モホウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジュンビ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蹴り上げ</t>
+    <rPh sb="0" eb="1">
+      <t>ケ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パンチ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>けり落とし</t>
+    <rPh sb="2" eb="3">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャスト回避</t>
+    <rPh sb="4" eb="6">
+      <t>カイヒ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ウィッチタイム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>空中食らい</t>
+    <rPh sb="0" eb="2">
+      <t>クウチュウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダメージ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カメラ揺らし</t>
+    <rPh sb="3" eb="4">
+      <t>ユ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -627,7 +703,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -638,6 +714,15 @@
     </font>
     <font>
       <sz val="6"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="128"/>
@@ -917,7 +1002,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1003,6 +1088,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3751,7 +3848,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C89A4258-94D6-44E2-BD96-6EB7C71AF1F2}">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
@@ -4425,9 +4522,94 @@
         <v>完成</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>78</v>
+      </c>
+      <c r="B29" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="B30" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="C30" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="D30" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="E30" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="F30" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="G30" s="32" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>2</v>
+      </c>
+      <c r="B31" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="B32" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B33" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B34" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B35" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B37" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
+        <v>20</v>
+      </c>
+      <c r="B38" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B39" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A40" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/SpingGame_2026.xlsx
+++ b/SpingGame_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\SpringGame_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SakamotoKou\Desktop\GitHub\SpringGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E508BE5-8032-4E84-BBFC-6394977E33AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F98057-9294-48A8-B98C-FBD7C556A239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="460" xr2:uid="{FD95E878-465A-49E4-912E-7153328F4E6C}"/>
+    <workbookView xWindow="-285" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="460" xr2:uid="{FD95E878-465A-49E4-912E-7153328F4E6C}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="82">
   <si>
     <t>2026年春作品コスト表</t>
     <rPh sb="4" eb="5">
@@ -616,85 +616,48 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>インターン作品</t>
-    <rPh sb="5" eb="7">
-      <t>サクヒン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ベヨネッタ模倣に向けたゲームの準備的な感じ</t>
-    <rPh sb="5" eb="7">
-      <t>モホウ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>ム</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ジュンビ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
+    <t>時間制限以内に敵を全員倒す</t>
+    <rPh sb="0" eb="2">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>セイゲン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>イナイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
       <t>テキ</t>
     </rPh>
-    <rPh sb="19" eb="20">
-      <t>カン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>蹴り上げ</t>
-    <rPh sb="0" eb="1">
-      <t>ケ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ア</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>パンチ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>けり落とし</t>
-    <rPh sb="2" eb="3">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ジャスト回避</t>
-    <rPh sb="4" eb="6">
-      <t>カイヒ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ウィッチタイム</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>HP</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>空中食らい</t>
+    <rPh sb="9" eb="12">
+      <t>ゼンインタオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲーム終了条件</t>
+    <rPh sb="3" eb="7">
+      <t>シュウリョウジョウケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死亡する</t>
     <rPh sb="0" eb="2">
-      <t>クウチュウ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ダメージ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>カメラ揺らし</t>
-    <rPh sb="3" eb="4">
-      <t>ユ</t>
+      <t>シボウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>時間制限に達する</t>
+    <rPh sb="0" eb="2">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>セイゲン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>タッ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -703,7 +666,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -725,6 +688,23 @@
       <color theme="0"/>
       <name val="游ゴシック"/>
       <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -767,7 +747,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -996,13 +976,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1090,21 +1085,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="11">
     <dxf>
@@ -3532,7 +3524,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -3848,10 +3840,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C89A4258-94D6-44E2-BD96-6EB7C71AF1F2}">
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.375" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="15.125" customWidth="1"/>
     <col min="5" max="5" width="12.125" customWidth="1"/>
@@ -4522,94 +4514,30 @@
         <v>完成</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A29" s="31" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A30" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="B29" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="B30" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="C30" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="D30" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="E30" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="F30" s="31" t="s">
-        <v>5</v>
-      </c>
-      <c r="G30" s="32" t="s">
-        <v>6</v>
-      </c>
+      <c r="B30" s="29"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>2</v>
-      </c>
-      <c r="B31" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B32" t="s">
+      <c r="A32" t="s">
         <v>81</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B33" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B34" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B35" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A36" t="s">
-        <v>11</v>
-      </c>
-      <c r="B36" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B37" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A38" t="s">
-        <v>20</v>
-      </c>
-      <c r="B38" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B39" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A40" t="s">
-        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/SpingGame_2026.xlsx
+++ b/SpingGame_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SakamotoKou\Desktop\GitHub\SpringGame_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\SpringGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F98057-9294-48A8-B98C-FBD7C556A239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D16A94BF-4A65-4AA3-BBC4-A1090B4CE4B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-285" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="460" xr2:uid="{FD95E878-465A-49E4-912E-7153328F4E6C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="460" xr2:uid="{FD95E878-465A-49E4-912E-7153328F4E6C}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="90">
   <si>
     <t>2026年春作品コスト表</t>
     <rPh sb="4" eb="5">
@@ -658,6 +658,110 @@
     </rPh>
     <rPh sb="5" eb="6">
       <t>タッ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ブラッシュアップすること(優先度順に)</t>
+    <rPh sb="13" eb="17">
+      <t>ユウセンドジュン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>音を付ける</t>
+    <rPh sb="0" eb="1">
+      <t>オト</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リザルトにプレスAボタン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シーン遷移後にエフェクトが残るバグを修正</t>
+    <rPh sb="3" eb="6">
+      <t>センイゴ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレスAボタン点滅</t>
+    <rPh sb="7" eb="9">
+      <t>テンメツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵に攻撃が当たった時のエフェクトの数を制限するか、それぞれ当たった敵の中心にエフェクトを出して、全員に当たった風にするか</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>カズ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>セイゲン</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>チュウシン</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ゼンイン</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>フウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵が吹っ飛ぶようにしたい</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ変えたい(ダサい)</t>
+    <rPh sb="4" eb="5">
+      <t>カ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1085,10 +1189,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1096,7 +1200,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="11">
     <dxf>
@@ -3524,7 +3628,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -3840,7 +3944,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C89A4258-94D6-44E2-BD96-6EB7C71AF1F2}">
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="30" bestFit="1" customWidth="1"/>
@@ -4538,6 +4642,46 @@
     <row r="32" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
         <v>81</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A34" s="31" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A35" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A39" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A40" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A41" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/SpingGame_2026.xlsx
+++ b/SpingGame_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\SpringGame_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SakamotoKou\Desktop\GitHub\SpringGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D16A94BF-4A65-4AA3-BBC4-A1090B4CE4B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74B0A432-AB0C-42A9-B297-B92E06D7B451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="460" xr2:uid="{FD95E878-465A-49E4-912E-7153328F4E6C}"/>
+    <workbookView xWindow="-285" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="460" xr2:uid="{FD95E878-465A-49E4-912E-7153328F4E6C}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="100">
   <si>
     <t>2026年春作品コスト表</t>
     <rPh sb="4" eb="5">
@@ -762,6 +762,105 @@
     <t>ステージ変えたい(ダサい)</t>
     <rPh sb="4" eb="5">
       <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>必要な音</t>
+    <rPh sb="0" eb="2">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>開始時のカウントダウン</t>
+    <rPh sb="0" eb="3">
+      <t>カイシジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はじめいっ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃した時のフィールドの音</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃が当たった時の音</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵が死ぬときの音</t>
+  </si>
+  <si>
+    <t>自分が攻撃を食らった時の音</t>
+    <rPh sb="0" eb="2">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>雷の音</t>
+    <rPh sb="0" eb="1">
+      <t>カミナリ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>点数が出てくるときの音</t>
+    <rPh sb="0" eb="2">
+      <t>テンスウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>デ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>走るときの音</t>
+    <rPh sb="0" eb="1">
+      <t>ハシ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>オト</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1200,7 +1299,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="11">
     <dxf>
@@ -3628,7 +3727,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -3944,7 +4043,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C89A4258-94D6-44E2-BD96-6EB7C71AF1F2}">
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="30" bestFit="1" customWidth="1"/>
@@ -4682,6 +4781,56 @@
     <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
         <v>88</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A43" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A44" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A45" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A46" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A47" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A48" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A49" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A50" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A51" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A52" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/SpingGame_2026.xlsx
+++ b/SpingGame_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SakamotoKou\Desktop\GitHub\SpringGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74B0A432-AB0C-42A9-B297-B92E06D7B451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AAD399E-8A4D-4C71-BCF0-9D7BECE9B8C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-285" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="460" xr2:uid="{FD95E878-465A-49E4-912E-7153328F4E6C}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="101">
   <si>
     <t>2026年春作品コスト表</t>
     <rPh sb="4" eb="5">
@@ -862,6 +862,10 @@
     <rPh sb="5" eb="6">
       <t>オト</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>✓</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -869,7 +873,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -910,6 +914,12 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1200,7 +1210,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1296,6 +1306,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4743,72 +4756,78 @@
         <v>81</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A34" s="31" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B44" s="32" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B45" s="32" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
         <v>95</v>
       </c>

--- a/SpingGame_2026.xlsx
+++ b/SpingGame_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SakamotoKou\Desktop\GitHub\SpringGame_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\SpringGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AAD399E-8A4D-4C71-BCF0-9D7BECE9B8C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA608067-2059-42C4-9685-012597AECFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-285" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="460" xr2:uid="{FD95E878-465A-49E4-912E-7153328F4E6C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="460" xr2:uid="{FD95E878-465A-49E4-912E-7153328F4E6C}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="101">
   <si>
     <t>2026年春作品コスト表</t>
     <rPh sb="4" eb="5">
@@ -1312,7 +1312,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="11">
     <dxf>
@@ -3740,7 +3740,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -4821,10 +4821,16 @@
       <c r="A46" t="s">
         <v>93</v>
       </c>
+      <c r="B46" s="32" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
         <v>94</v>
+      </c>
+      <c r="B47" s="32" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.4">

--- a/SpingGame_2026.xlsx
+++ b/SpingGame_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\SpringGame_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SakamotoKou\Desktop\GitHub\SpringGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA608067-2059-42C4-9685-012597AECFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="460" xr2:uid="{FD95E878-465A-49E4-912E-7153328F4E6C}"/>
+    <workbookView xWindow="6675" yWindow="-14025" windowWidth="21600" windowHeight="11295" tabRatio="460" xr2:uid="{FD95E878-465A-49E4-912E-7153328F4E6C}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -1312,7 +1312,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="11">
     <dxf>
@@ -3740,7 +3740,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>

--- a/SpingGame_2026.xlsx
+++ b/SpingGame_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SakamotoKou\Desktop\GitHub\SpringGame_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\SpringGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA608067-2059-42C4-9685-012597AECFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E472689D-C9BE-40A9-8AA5-4AD0F4F724E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6675" yWindow="-14025" windowWidth="21600" windowHeight="11295" tabRatio="460" xr2:uid="{FD95E878-465A-49E4-912E-7153328F4E6C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="460" xr2:uid="{FD95E878-465A-49E4-912E-7153328F4E6C}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="101">
   <si>
     <t>2026年春作品コスト表</t>
     <rPh sb="4" eb="5">
@@ -1312,7 +1312,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="11">
     <dxf>
@@ -3740,7 +3740,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -4837,25 +4837,40 @@
       <c r="A48" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B48" s="32" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B49" s="32" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B50" s="32" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B51" s="32" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
         <v>99</v>
+      </c>
+      <c r="B52" s="32" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/SpingGame_2026.xlsx
+++ b/SpingGame_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\SpringGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E472689D-C9BE-40A9-8AA5-4AD0F4F724E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8227CD-FAA6-4A44-90C2-D055EDCFDB7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="460" xr2:uid="{FD95E878-465A-49E4-912E-7153328F4E6C}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="100">
   <si>
     <t>2026年春作品コスト表</t>
     <rPh sb="4" eb="5">
@@ -665,16 +665,6 @@
     <t>ブラッシュアップすること(優先度順に)</t>
     <rPh sb="13" eb="17">
       <t>ユウセンドジュン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>音を付ける</t>
-    <rPh sb="0" eb="1">
-      <t>オト</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ツ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4056,10 +4046,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C89A4258-94D6-44E2-BD96-6EB7C71AF1F2}">
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="30" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="114.625" customWidth="1"/>
     <col min="2" max="2" width="25.375" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="15.125" customWidth="1"/>
     <col min="5" max="5" width="12.125" customWidth="1"/>
@@ -4756,121 +4746,104 @@
         <v>81</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A34" s="31" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
+        <v>88</v>
+      </c>
+      <c r="B35" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A36" t="s">
+      <c r="B36" t="s">
+        <v>90</v>
+      </c>
+      <c r="C36" s="32" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A37" t="s">
+      <c r="B37" t="s">
+        <v>91</v>
+      </c>
+      <c r="C37" s="32" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A38" t="s">
+      <c r="B38" t="s">
+        <v>92</v>
+      </c>
+      <c r="C38" s="32" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A39" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A39" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B39" t="s">
+        <v>93</v>
+      </c>
+      <c r="C39" s="32" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A41" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A43" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A44" t="s">
-        <v>91</v>
-      </c>
-      <c r="B44" s="32" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A45" t="s">
-        <v>92</v>
-      </c>
-      <c r="B45" s="32" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A46" t="s">
-        <v>93</v>
-      </c>
-      <c r="B46" s="32" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A47" t="s">
+      <c r="B40" t="s">
         <v>94</v>
       </c>
-      <c r="B47" s="32" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A48" t="s">
+      <c r="C40" s="32" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B41" t="s">
         <v>95</v>
       </c>
-      <c r="B48" s="32" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A49" t="s">
+      <c r="C41" s="32" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B42" t="s">
         <v>96</v>
       </c>
-      <c r="B49" s="32" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A50" t="s">
+      <c r="C42" s="32" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B43" t="s">
         <v>97</v>
       </c>
-      <c r="B50" s="32" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A51" t="s">
+      <c r="C43" s="32" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B44" t="s">
         <v>98</v>
       </c>
-      <c r="B51" s="32" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A52" t="s">
+      <c r="C44" s="32" t="s">
         <v>99</v>
-      </c>
-      <c r="B52" s="32" t="s">
-        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/SpingGame_2026.xlsx
+++ b/SpingGame_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\SpringGame_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SakamotoKou\Desktop\GitHub\SpringGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8227CD-FAA6-4A44-90C2-D055EDCFDB7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D85C0211-D2E2-46D1-AB61-B4723A1105AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="460" xr2:uid="{FD95E878-465A-49E4-912E-7153328F4E6C}"/>
+    <workbookView xWindow="6675" yWindow="-14025" windowWidth="21600" windowHeight="11295" tabRatio="460" xr2:uid="{FD95E878-465A-49E4-912E-7153328F4E6C}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="98">
   <si>
     <t>2026年春作品コスト表</t>
     <rPh sb="4" eb="5">
@@ -669,23 +669,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>リザルトにプレスAボタン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>シーン遷移後にエフェクトが残るバグを修正</t>
-    <rPh sb="3" eb="6">
-      <t>センイゴ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ノコ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>シュウセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>プレスAボタン点滅</t>
     <rPh sb="7" eb="9">
       <t>テンメツ</t>
@@ -693,49 +676,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>敵に攻撃が当たった時のエフェクトの数を制限するか、それぞれ当たった敵の中心にエフェクトを出して、全員に当たった風にするか</t>
-    <rPh sb="0" eb="1">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>コウゲキ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>トキ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>カズ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>セイゲン</t>
-    </rPh>
-    <rPh sb="29" eb="30">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="33" eb="34">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>チュウシン</t>
-    </rPh>
-    <rPh sb="44" eb="45">
-      <t>ダ</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>ゼンイン</t>
-    </rPh>
-    <rPh sb="51" eb="52">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="55" eb="56">
-      <t>フウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>敵が吹っ飛ぶようにしたい</t>
     <rPh sb="0" eb="1">
       <t>テキ</t>
@@ -856,6 +796,22 @@
   </si>
   <si>
     <t>✓</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>文字の桁が増えたときに場所がずれないようにする</t>
+    <rPh sb="0" eb="2">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ケタ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>バショ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1302,7 +1258,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="11">
     <dxf>
@@ -3730,7 +3686,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -4753,10 +4709,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B35" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.4">
@@ -4764,10 +4720,10 @@
         <v>83</v>
       </c>
       <c r="B36" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C36" s="32" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.4">
@@ -4775,75 +4731,69 @@
         <v>84</v>
       </c>
       <c r="B37" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C37" s="32" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B38" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C38" s="32" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A39" t="s">
-        <v>86</v>
-      </c>
       <c r="B39" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C39" s="32" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A40" t="s">
-        <v>87</v>
-      </c>
       <c r="B40" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C40" s="32" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B41" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C41" s="32" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B42" t="s">
+        <v>93</v>
+      </c>
+      <c r="C42" s="32" t="s">
         <v>96</v>
-      </c>
-      <c r="C42" s="32" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B43" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C43" s="32" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B44" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C44" s="32" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/SpingGame_2026.xlsx
+++ b/SpingGame_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SakamotoKou\Desktop\GitHub\SpringGame_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\SpringGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D85C0211-D2E2-46D1-AB61-B4723A1105AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{173ED329-2CE5-41A7-BE18-44721CCDBDC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6675" yWindow="-14025" windowWidth="21600" windowHeight="11295" tabRatio="460" xr2:uid="{FD95E878-465A-49E4-912E-7153328F4E6C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="460" xr2:uid="{FD95E878-465A-49E4-912E-7153328F4E6C}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="97">
   <si>
     <t>2026年春作品コスト表</t>
     <rPh sb="4" eb="5">
@@ -665,13 +665,6 @@
     <t>ブラッシュアップすること(優先度順に)</t>
     <rPh sb="13" eb="17">
       <t>ユウセンドジュン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>プレスAボタン点滅</t>
-    <rPh sb="7" eb="9">
-      <t>テンメツ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1258,7 +1251,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="11">
     <dxf>
@@ -3686,7 +3679,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -4709,10 +4702,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
+        <v>84</v>
+      </c>
+      <c r="B35" t="s">
         <v>85</v>
-      </c>
-      <c r="B35" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.4">
@@ -4720,80 +4713,77 @@
         <v>83</v>
       </c>
       <c r="B36" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C36" s="32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="B37" t="s">
+        <v>87</v>
+      </c>
+      <c r="C37" s="32" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B38" t="s">
         <v>88</v>
       </c>
-      <c r="C37" s="32" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A38" t="s">
-        <v>97</v>
-      </c>
-      <c r="B38" t="s">
-        <v>89</v>
-      </c>
       <c r="C38" s="32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B39" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C39" s="32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B40" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C40" s="32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B41" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C41" s="32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C42" s="32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B43" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C43" s="32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B44" t="s">
+        <v>94</v>
+      </c>
+      <c r="C44" s="32" t="s">
         <v>95</v>
-      </c>
-      <c r="C44" s="32" t="s">
-        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/SpingGame_2026.xlsx
+++ b/SpingGame_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\SpringGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{173ED329-2CE5-41A7-BE18-44721CCDBDC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8CABE73-D697-4C59-83B6-E849A245AABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="460" xr2:uid="{FD95E878-465A-49E4-912E-7153328F4E6C}"/>
+    <workbookView xWindow="6630" yWindow="1995" windowWidth="9435" windowHeight="10800" tabRatio="460" xr2:uid="{FD95E878-465A-49E4-912E-7153328F4E6C}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="98">
   <si>
     <t>2026年春作品コスト表</t>
     <rPh sb="4" eb="5">
@@ -804,6 +804,19 @@
     </rPh>
     <rPh sb="11" eb="13">
       <t>バショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>全員倒したときの演出</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンイン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>タオ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>エンシュツ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4702,7 +4715,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="B35" t="s">
         <v>85</v>
@@ -4710,7 +4723,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B36" t="s">
         <v>86</v>
@@ -4721,7 +4734,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="B37" t="s">
         <v>87</v>
@@ -4731,6 +4744,9 @@
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
+        <v>96</v>
+      </c>
       <c r="B38" t="s">
         <v>88</v>
       </c>
